--- a/Lab_4/data/partB/param_optimization_process/v100_k10_s100_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v100_k10_s100_results.xlsx
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>7</v>
@@ -539,19 +539,19 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
         <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>11</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -646,22 +646,22 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -677,16 +677,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
@@ -698,13 +698,13 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -716,7 +716,7 @@
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -726,43 +726,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -787,40 +787,40 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>53</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -830,49 +830,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -882,28 +882,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -915,16 +915,16 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -995,34 +995,34 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>18</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" t="n">
-        <v>34</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1038,19 +1038,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1059,25 +1059,25 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1093,40 +1093,40 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
         <v>8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -1142,49 +1142,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -1197,16 +1197,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1218,22 +1218,22 @@
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1249,25 +1249,25 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
         <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
@@ -1276,19 +1276,19 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
-        <v>3</v>
-      </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13881,7 +13881,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14731,7 +14731,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20596,7 +20596,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21905,7 +21905,7 @@
       </c>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25237,7 +25237,7 @@
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25322,7 +25322,7 @@
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26002,7 +26002,7 @@
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26223,7 +26223,7 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26648,7 +26648,7 @@
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
